--- a/diseases/d042/1995-1999.xlsx
+++ b/diseases/d042/1995-1999.xlsx
@@ -765,9 +765,6 @@
       <c r="O2" t="n">
         <v>0</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="S2" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1158,9 +1155,6 @@
       <c r="O4" t="n">
         <v>0</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="S4" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1551,9 +1545,6 @@
       <c r="O6" t="n">
         <v>0</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="S6" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1944,9 +1935,6 @@
       <c r="O8" t="n">
         <v>0</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="S8" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -2337,9 +2325,6 @@
       <c r="O10" t="n">
         <v>0</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="S10" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -2730,9 +2715,6 @@
       <c r="O12" t="n">
         <v>0</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="S12" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -3123,9 +3105,6 @@
       <c r="O14" t="n">
         <v>0</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="S14" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -3516,9 +3495,6 @@
       <c r="O16" t="n">
         <v>0</v>
       </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
       <c r="S16" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -3909,9 +3885,6 @@
       <c r="O18" t="n">
         <v>0</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="S18" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -4302,9 +4275,6 @@
       <c r="O20" t="n">
         <v>0</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="S20" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -4695,9 +4665,6 @@
       <c r="O22" t="n">
         <v>1</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="S22" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -5088,9 +5055,6 @@
       <c r="O24" t="n">
         <v>0</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="S24" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -5481,9 +5445,6 @@
       <c r="O26" t="n">
         <v>0</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
       <c r="S26" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -5874,9 +5835,6 @@
       <c r="O28" t="n">
         <v>0</v>
       </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
       <c r="S28" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -6267,9 +6225,6 @@
       <c r="O30" t="n">
         <v>0</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="S30" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -6660,9 +6615,6 @@
       <c r="O32" t="n">
         <v>0</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
       <c r="S32" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -7053,9 +7005,6 @@
       <c r="O34" t="n">
         <v>0</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
       <c r="S34" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -7446,9 +7395,6 @@
       <c r="O36" t="n">
         <v>0</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
       <c r="S36" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -7839,9 +7785,6 @@
       <c r="O38" t="n">
         <v>0</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="S38" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -8232,9 +8175,6 @@
       <c r="O40" t="n">
         <v>0</v>
       </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
       <c r="S40" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -8625,9 +8565,6 @@
       <c r="O42" t="n">
         <v>1</v>
       </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
       <c r="S42" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -9018,9 +8955,6 @@
       <c r="O44" t="n">
         <v>0</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="S44" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -9411,9 +9345,6 @@
       <c r="O46" t="n">
         <v>1</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
       <c r="S46" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -9804,9 +9735,6 @@
       <c r="O48" t="n">
         <v>0</v>
       </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
       <c r="S48" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -10342,9 +10270,6 @@
       <c r="O51" t="n">
         <v>0</v>
       </c>
-      <c r="Q51" t="n">
-        <v>0</v>
-      </c>
       <c r="S51" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -10735,9 +10660,6 @@
       <c r="O53" t="n">
         <v>0</v>
       </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
       <c r="S53" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -11273,9 +11195,6 @@
       <c r="O56" t="n">
         <v>0</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="S56" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -11811,9 +11730,6 @@
       <c r="O59" t="n">
         <v>0</v>
       </c>
-      <c r="Q59" t="n">
-        <v>0</v>
-      </c>
       <c r="S59" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -12349,9 +12265,6 @@
       <c r="O62" t="n">
         <v>0</v>
       </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
       <c r="S62" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -12887,9 +12800,6 @@
       <c r="O65" t="n">
         <v>0</v>
       </c>
-      <c r="Q65" t="n">
-        <v>0</v>
-      </c>
       <c r="S65" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -13425,9 +13335,6 @@
       <c r="O68" t="n">
         <v>0</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="S68" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -13963,9 +13870,6 @@
       <c r="O71" t="n">
         <v>0</v>
       </c>
-      <c r="Q71" t="n">
-        <v>0</v>
-      </c>
       <c r="S71" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -14501,9 +14405,6 @@
       <c r="O74" t="n">
         <v>0</v>
       </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
       <c r="S74" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -15039,9 +14940,6 @@
       <c r="O77" t="n">
         <v>0</v>
       </c>
-      <c r="Q77" t="n">
-        <v>0</v>
-      </c>
       <c r="S77" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -15577,9 +15475,6 @@
       <c r="O80" t="n">
         <v>0</v>
       </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
       <c r="S80" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -16115,9 +16010,6 @@
       <c r="O83" t="n">
         <v>1</v>
       </c>
-      <c r="Q83" t="n">
-        <v>0</v>
-      </c>
       <c r="S83" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -16653,9 +16545,6 @@
       <c r="O86" t="n">
         <v>0</v>
       </c>
-      <c r="Q86" t="n">
-        <v>0</v>
-      </c>
       <c r="S86" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -17191,9 +17080,6 @@
       <c r="O89" t="n">
         <v>0</v>
       </c>
-      <c r="Q89" t="n">
-        <v>0</v>
-      </c>
       <c r="S89" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -19322,9 +19208,6 @@
         <v>0</v>
       </c>
       <c r="O103" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q103" t="n">
         <v>0</v>
       </c>
       <c r="S103" t="inlineStr">

--- a/diseases/d042/1995-1999.xlsx
+++ b/diseases/d042/1995-1999.xlsx
@@ -721,12 +721,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -772,12 +772,12 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_503_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D64_ANNUAL</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -797,7 +797,7 @@
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_503_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D64_ANNUAL</t>
         </is>
       </c>
       <c r="AT2" t="n">
@@ -810,42 +810,42 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -877,12 +877,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -916,29 +916,29 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_503_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D64_ANNUAL</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_503_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D64_ANNUAL</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_CA_PHAC_CNDSS</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>Lepra</t>
+          <t>Leprosy</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -948,12 +948,12 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>provincial_territorial_voluntary_notifications_national</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:CA:national</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -998,12 +998,12 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
@@ -1031,7 +1031,7 @@
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_503_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D64_ANNUAL</t>
         </is>
       </c>
       <c r="AT3" t="n">
@@ -1044,42 +1044,42 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -1141,12 +1141,12 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>1995-02-01</t>
+          <t>1995-01-01</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>1995-02</t>
+          <t>1995-01</t>
         </is>
       </c>
       <c r="N4" t="n">
@@ -1297,12 +1297,12 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>1995-02-01</t>
+          <t>1995-01-01</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>1995-02</t>
+          <t>1995-01</t>
         </is>
       </c>
       <c r="N5" t="n">
@@ -1531,12 +1531,12 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>1995-03-01</t>
+          <t>1995-02-01</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>1995-03</t>
+          <t>1995-02</t>
         </is>
       </c>
       <c r="N6" t="n">
@@ -1687,12 +1687,12 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>1995-03-01</t>
+          <t>1995-02-01</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>1995-03</t>
+          <t>1995-02</t>
         </is>
       </c>
       <c r="N7" t="n">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>1995-04-01</t>
+          <t>1995-03-01</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>1995-04</t>
+          <t>1995-03</t>
         </is>
       </c>
       <c r="N8" t="n">
@@ -2077,12 +2077,12 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>1995-04-01</t>
+          <t>1995-03-01</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>1995-04</t>
+          <t>1995-03</t>
         </is>
       </c>
       <c r="N9" t="n">
@@ -2311,12 +2311,12 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>1995-05-01</t>
+          <t>1995-04-01</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>1995-05</t>
+          <t>1995-04</t>
         </is>
       </c>
       <c r="N10" t="n">
@@ -2467,12 +2467,12 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>1995-05-01</t>
+          <t>1995-04-01</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>1995-05</t>
+          <t>1995-04</t>
         </is>
       </c>
       <c r="N11" t="n">
@@ -2701,12 +2701,12 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>1995-06-01</t>
+          <t>1995-05-01</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>1995-06</t>
+          <t>1995-05</t>
         </is>
       </c>
       <c r="N12" t="n">
@@ -2857,12 +2857,12 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>1995-06-01</t>
+          <t>1995-05-01</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>1995-06</t>
+          <t>1995-05</t>
         </is>
       </c>
       <c r="N13" t="n">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>1995-07-01</t>
+          <t>1995-06-01</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>1995-07</t>
+          <t>1995-06</t>
         </is>
       </c>
       <c r="N14" t="n">
@@ -3247,12 +3247,12 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>1995-07-01</t>
+          <t>1995-06-01</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>1995-07</t>
+          <t>1995-06</t>
         </is>
       </c>
       <c r="N15" t="n">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>1995-08-01</t>
+          <t>1995-07-01</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>1995-08</t>
+          <t>1995-07</t>
         </is>
       </c>
       <c r="N16" t="n">
@@ -3637,12 +3637,12 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>1995-08-01</t>
+          <t>1995-07-01</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>1995-08</t>
+          <t>1995-07</t>
         </is>
       </c>
       <c r="N17" t="n">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>1995-09-01</t>
+          <t>1995-08-01</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>1995-09</t>
+          <t>1995-08</t>
         </is>
       </c>
       <c r="N18" t="n">
@@ -4027,12 +4027,12 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>1995-09-01</t>
+          <t>1995-08-01</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>1995-09</t>
+          <t>1995-08</t>
         </is>
       </c>
       <c r="N19" t="n">
@@ -4261,12 +4261,12 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>1995-10-01</t>
+          <t>1995-09-01</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>1995-10</t>
+          <t>1995-09</t>
         </is>
       </c>
       <c r="N20" t="n">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>1995-10-01</t>
+          <t>1995-09-01</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>1995-10</t>
+          <t>1995-09</t>
         </is>
       </c>
       <c r="N21" t="n">
@@ -4651,19 +4651,19 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>1995-11-01</t>
+          <t>1995-10-01</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>1995-11</t>
+          <t>1995-10</t>
         </is>
       </c>
       <c r="N22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -4807,19 +4807,19 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>1995-11-01</t>
+          <t>1995-10-01</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>1995-11</t>
+          <t>1995-10</t>
         </is>
       </c>
       <c r="N23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U23" t="inlineStr">
         <is>
@@ -5041,19 +5041,19 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>1995-12-01</t>
+          <t>1995-11-01</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>1995-12</t>
+          <t>1995-11</t>
         </is>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -5197,19 +5197,19 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>1995-12-01</t>
+          <t>1995-11-01</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>1995-12</t>
+          <t>1995-11</t>
         </is>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U25" t="inlineStr">
         <is>
@@ -5431,12 +5431,12 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>1996-01-01</t>
+          <t>1995-12-01</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>1996-01</t>
+          <t>1995-12</t>
         </is>
       </c>
       <c r="N26" t="n">
@@ -5587,12 +5587,12 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>1996-01-01</t>
+          <t>1995-12-01</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>1996-01</t>
+          <t>1995-12</t>
         </is>
       </c>
       <c r="N27" t="n">
@@ -5791,12 +5791,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -5821,19 +5821,19 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>1996-02-01</t>
+          <t>1996-01-01</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>1996-02</t>
+          <t>1996-01</t>
         </is>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -5842,12 +5842,12 @@
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_503_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D64_ANNUAL</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
@@ -5867,7 +5867,7 @@
       </c>
       <c r="AS28" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_503_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D64_ANNUAL</t>
         </is>
       </c>
       <c r="AT28" t="n">
@@ -5880,42 +5880,42 @@
       </c>
       <c r="AV28" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB28" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC28" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -5947,12 +5947,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -5977,38 +5977,38 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>1996-02-01</t>
+          <t>1996-01-01</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>1996-02</t>
+          <t>1996-01</t>
         </is>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_503_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D64_ANNUAL</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_503_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D64_ANNUAL</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_CA_PHAC_CNDSS</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>Lepra</t>
+          <t>Leprosy</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>provincial_territorial_voluntary_notifications_national</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
@@ -6033,7 +6033,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:CA:national</t>
         </is>
       </c>
       <c r="AD29" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
         </is>
       </c>
       <c r="AM29" t="inlineStr">
@@ -6101,7 +6101,7 @@
       </c>
       <c r="AS29" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_503_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D64_ANNUAL</t>
         </is>
       </c>
       <c r="AT29" t="n">
@@ -6114,42 +6114,42 @@
       </c>
       <c r="AV29" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB29" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC29" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -6211,12 +6211,12 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>1996-03-01</t>
+          <t>1996-01-01</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>1996-03</t>
+          <t>1996-01</t>
         </is>
       </c>
       <c r="N30" t="n">
@@ -6367,12 +6367,12 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>1996-03-01</t>
+          <t>1996-01-01</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>1996-03</t>
+          <t>1996-01</t>
         </is>
       </c>
       <c r="N31" t="n">
@@ -6601,12 +6601,12 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>1996-04-01</t>
+          <t>1996-02-01</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>1996-04</t>
+          <t>1996-02</t>
         </is>
       </c>
       <c r="N32" t="n">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>1996-04-01</t>
+          <t>1996-02-01</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>1996-04</t>
+          <t>1996-02</t>
         </is>
       </c>
       <c r="N33" t="n">
@@ -6991,12 +6991,12 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>1996-05-01</t>
+          <t>1996-03-01</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>1996-05</t>
+          <t>1996-03</t>
         </is>
       </c>
       <c r="N34" t="n">
@@ -7147,12 +7147,12 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>1996-05-01</t>
+          <t>1996-03-01</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>1996-05</t>
+          <t>1996-03</t>
         </is>
       </c>
       <c r="N35" t="n">
@@ -7381,12 +7381,12 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>1996-06-01</t>
+          <t>1996-04-01</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>1996-06</t>
+          <t>1996-04</t>
         </is>
       </c>
       <c r="N36" t="n">
@@ -7537,12 +7537,12 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>1996-06-01</t>
+          <t>1996-04-01</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>1996-06</t>
+          <t>1996-04</t>
         </is>
       </c>
       <c r="N37" t="n">
@@ -7771,12 +7771,12 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>1996-07-01</t>
+          <t>1996-05-01</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>1996-07</t>
+          <t>1996-05</t>
         </is>
       </c>
       <c r="N38" t="n">
@@ -7927,12 +7927,12 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>1996-07-01</t>
+          <t>1996-05-01</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>1996-07</t>
+          <t>1996-05</t>
         </is>
       </c>
       <c r="N39" t="n">
@@ -8161,12 +8161,12 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>1996-08-01</t>
+          <t>1996-06-01</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>1996-08</t>
+          <t>1996-06</t>
         </is>
       </c>
       <c r="N40" t="n">
@@ -8317,12 +8317,12 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>1996-08-01</t>
+          <t>1996-06-01</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>1996-08</t>
+          <t>1996-06</t>
         </is>
       </c>
       <c r="N41" t="n">
@@ -8551,19 +8551,19 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>1996-09-01</t>
+          <t>1996-07-01</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>1996-09</t>
+          <t>1996-07</t>
         </is>
       </c>
       <c r="N42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -8707,19 +8707,19 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>1996-09-01</t>
+          <t>1996-07-01</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>1996-09</t>
+          <t>1996-07</t>
         </is>
       </c>
       <c r="N43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U43" t="inlineStr">
         <is>
@@ -8941,12 +8941,12 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>1996-10-01</t>
+          <t>1996-08-01</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>1996-10</t>
+          <t>1996-08</t>
         </is>
       </c>
       <c r="N44" t="n">
@@ -9097,12 +9097,12 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>1996-10-01</t>
+          <t>1996-08-01</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>1996-10</t>
+          <t>1996-08</t>
         </is>
       </c>
       <c r="N45" t="n">
@@ -9331,12 +9331,12 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>1996-11-01</t>
+          <t>1996-09-01</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>1996-11</t>
+          <t>1996-09</t>
         </is>
       </c>
       <c r="N46" t="n">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>1996-11-01</t>
+          <t>1996-09-01</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>1996-11</t>
+          <t>1996-09</t>
         </is>
       </c>
       <c r="N47" t="n">
@@ -9721,12 +9721,12 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>1996-12-01</t>
+          <t>1996-10-01</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>1996-12</t>
+          <t>1996-10</t>
         </is>
       </c>
       <c r="N48" t="n">
@@ -9877,12 +9877,12 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>1996-12-01</t>
+          <t>1996-10-01</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>1996-12</t>
+          <t>1996-10</t>
         </is>
       </c>
       <c r="N49" t="n">
@@ -10081,12 +10081,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -10111,90 +10111,101 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>1997-01-01</t>
+          <t>1996-11-01</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>1997-01</t>
+          <t>1996-11</t>
         </is>
       </c>
       <c r="N50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O50" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
           <t>missing_population</t>
         </is>
       </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_503_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP50" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR50" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS50" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ50" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS50" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_503_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU50" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV50" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA50" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB50" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC50" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -10221,17 +10232,17 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -10256,34 +10267,112 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>1997-01-01</t>
+          <t>1996-11-01</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>1997-01</t>
+          <t>1996-11</t>
         </is>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O51" t="n">
-        <v>0</v>
-      </c>
-      <c r="S51" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_LEPROSY_ANNUAL</t>
+          <t>SER_NO_FHI_503_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_503_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>Lepra</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>annual</t>
-        </is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD51" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE51" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF51" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG51" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM51" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN51" t="b">
+        <v>1</v>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
@@ -10302,7 +10391,7 @@
       </c>
       <c r="AS51" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_LEPROSY_ANNUAL</t>
+          <t>SER_NO_FHI_503_MONTHLY</t>
         </is>
       </c>
       <c r="AT51" t="n">
@@ -10315,42 +10404,42 @@
       </c>
       <c r="AV51" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA51" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB51" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC51" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -10377,17 +10466,17 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -10412,12 +10501,12 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>1997-01-01</t>
+          <t>1996-12-01</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>1997-01</t>
+          <t>1996-12</t>
         </is>
       </c>
       <c r="N52" t="n">
@@ -10426,98 +10515,20 @@
       <c r="O52" t="n">
         <v>0</v>
       </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_LEPROSY_ANNUAL</t>
-        </is>
-      </c>
-      <c r="V52" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_LEPROSY_ANNUAL</t>
-        </is>
-      </c>
-      <c r="W52" t="inlineStr">
-        <is>
-          <t>SRC_IS_DOH_HISTORY</t>
-        </is>
-      </c>
-      <c r="X52" t="inlineStr">
-        <is>
-          <t>Holdsveiki</t>
-        </is>
-      </c>
-      <c r="Y52" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>national_registry_notifications</t>
+          <t>SER_NO_FHI_503_MONTHLY</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>annual</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>country:IS:national</t>
-        </is>
-      </c>
-      <c r="AD52" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE52" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF52" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG52" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH52" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI52" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ52" t="inlineStr">
-        <is>
-          <t>IS_DOH_historical_registry_annual</t>
-        </is>
-      </c>
-      <c r="AK52" t="inlineStr">
-        <is>
-          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
-        </is>
-      </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN52" t="b">
-        <v>1</v>
+          <t>monthly</t>
+        </is>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
@@ -10536,7 +10547,7 @@
       </c>
       <c r="AS52" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_LEPROSY_ANNUAL</t>
+          <t>SER_NO_FHI_503_MONTHLY</t>
         </is>
       </c>
       <c r="AT52" t="n">
@@ -10549,42 +10560,42 @@
       </c>
       <c r="AV52" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA52" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB52" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC52" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -10611,7 +10622,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -10646,12 +10657,12 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>1997-01-01</t>
+          <t>1996-12-01</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>1997-01</t>
+          <t>1996-12</t>
         </is>
       </c>
       <c r="N53" t="n">
@@ -10660,20 +10671,98 @@
       <c r="O53" t="n">
         <v>0</v>
       </c>
-      <c r="S53" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="U53" t="inlineStr">
         <is>
           <t>SER_NO_FHI_503_MONTHLY</t>
         </is>
       </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_503_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>Lepra</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD53" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE53" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF53" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG53" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI53" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM53" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN53" t="b">
+        <v>1</v>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
@@ -10767,17 +10856,17 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -10811,103 +10900,25 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O54" t="n">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_503_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V54" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_503_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W54" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X54" t="inlineStr">
-        <is>
-          <t>Lepra</t>
-        </is>
-      </c>
-      <c r="Y54" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>SER_CA_PHAC_CNDSS_D64_ANNUAL</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD54" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE54" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF54" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG54" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH54" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI54" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ54" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK54" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN54" t="b">
-        <v>1</v>
+          <t>annual</t>
+        </is>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
@@ -10926,7 +10937,7 @@
       </c>
       <c r="AS54" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_503_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D64_ANNUAL</t>
         </is>
       </c>
       <c r="AT54" t="n">
@@ -10939,42 +10950,42 @@
       </c>
       <c r="AV54" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA54" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB54" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC54" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -11001,17 +11012,17 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -11036,90 +11047,179 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>1997-02-01</t>
+          <t>1997-01-01</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>1997-02</t>
+          <t>1997-01</t>
         </is>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O55" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q55" t="n">
-        <v>0</v>
-      </c>
-      <c r="S55" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
+        <v>4</v>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D64_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D64_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>SRC_CA_PHAC_CNDSS</t>
+        </is>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>Leprosy</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>provincial_territorial_voluntary_notifications_national</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>country:CA:national</t>
+        </is>
+      </c>
+      <c r="AD55" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE55" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF55" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG55" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH55" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI55" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
+        </is>
+      </c>
+      <c r="AM55" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN55" t="b">
+        <v>1</v>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP55" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR55" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS55" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ55" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS55" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D64_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU55" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV55" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB55" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC55" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -11151,12 +11251,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -11181,18 +11281,21 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>1997-02-01</t>
+          <t>1997-01-01</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>1997-02</t>
+          <t>1997-01</t>
         </is>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O56" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q56" t="n">
         <v>0</v>
       </c>
       <c r="S56" t="inlineStr">
@@ -11200,82 +11303,68 @@
           <t>missing_population</t>
         </is>
       </c>
-      <c r="U56" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_503_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA56" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO56" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP56" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ56" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS56" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_503_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR56" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS56" t="inlineStr"/>
       <c r="AT56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU56" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV56" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA56" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB56" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC56" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -11302,17 +11391,17 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -11337,12 +11426,12 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>1997-02-01</t>
+          <t>1997-01-01</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>1997-02</t>
+          <t>1997-01</t>
         </is>
       </c>
       <c r="N57" t="n">
@@ -11351,98 +11440,20 @@
       <c r="O57" t="n">
         <v>0</v>
       </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_503_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V57" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_503_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W57" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X57" t="inlineStr">
-        <is>
-          <t>Lepra</t>
-        </is>
-      </c>
-      <c r="Y57" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>SER_IS_HISTORY_LEPROSY_ANNUAL</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD57" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE57" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF57" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG57" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH57" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI57" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ57" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK57" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM57" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN57" t="b">
-        <v>1</v>
+          <t>annual</t>
+        </is>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
@@ -11461,7 +11472,7 @@
       </c>
       <c r="AS57" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_503_MONTHLY</t>
+          <t>SER_IS_HISTORY_LEPROSY_ANNUAL</t>
         </is>
       </c>
       <c r="AT57" t="n">
@@ -11474,42 +11485,42 @@
       </c>
       <c r="AV57" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA57" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB57" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC57" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -11536,17 +11547,17 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -11571,90 +11582,179 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>1997-03-01</t>
+          <t>1997-01-01</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>1997-03</t>
+          <t>1997-01</t>
         </is>
       </c>
       <c r="N58" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O58" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
-      <c r="S58" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_LEPROSY_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_LEPROSY_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_HISTORY</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>Holdsveiki</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>national_registry_notifications</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD58" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE58" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF58" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG58" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH58" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI58" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ58" t="inlineStr">
+        <is>
+          <t>IS_DOH_historical_registry_annual</t>
+        </is>
+      </c>
+      <c r="AK58" t="inlineStr">
+        <is>
+          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM58" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN58" t="b">
+        <v>1</v>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP58" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR58" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS58" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ58" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS58" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_LEPROSY_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU58" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV58" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA58" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB58" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC58" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -11716,12 +11816,12 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>1997-03-01</t>
+          <t>1997-01-01</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>1997-03</t>
+          <t>1997-01</t>
         </is>
       </c>
       <c r="N59" t="n">
@@ -11872,12 +11972,12 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>1997-03-01</t>
+          <t>1997-01-01</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>1997-03</t>
+          <t>1997-01</t>
         </is>
       </c>
       <c r="N60" t="n">
@@ -12106,19 +12206,19 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>1997-04-01</t>
+          <t>1997-02-01</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>1997-04</t>
+          <t>1997-02</t>
         </is>
       </c>
       <c r="N61" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O61" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
@@ -12251,12 +12351,12 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>1997-04-01</t>
+          <t>1997-02-01</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>1997-04</t>
+          <t>1997-02</t>
         </is>
       </c>
       <c r="N62" t="n">
@@ -12407,12 +12507,12 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>1997-04-01</t>
+          <t>1997-02-01</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>1997-04</t>
+          <t>1997-02</t>
         </is>
       </c>
       <c r="N63" t="n">
@@ -12641,19 +12741,19 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>1997-05-01</t>
+          <t>1997-03-01</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>1997-05</t>
+          <t>1997-03</t>
         </is>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O64" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q64" t="n">
         <v>0</v>
@@ -12786,12 +12886,12 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>1997-05-01</t>
+          <t>1997-03-01</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>1997-05</t>
+          <t>1997-03</t>
         </is>
       </c>
       <c r="N65" t="n">
@@ -12942,12 +13042,12 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>1997-05-01</t>
+          <t>1997-03-01</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>1997-05</t>
+          <t>1997-03</t>
         </is>
       </c>
       <c r="N66" t="n">
@@ -13176,19 +13276,19 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>1997-06-01</t>
+          <t>1997-04-01</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>1997-06</t>
+          <t>1997-04</t>
         </is>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O67" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q67" t="n">
         <v>0</v>
@@ -13321,12 +13421,12 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>1997-06-01</t>
+          <t>1997-04-01</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>1997-06</t>
+          <t>1997-04</t>
         </is>
       </c>
       <c r="N68" t="n">
@@ -13477,12 +13577,12 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>1997-06-01</t>
+          <t>1997-04-01</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>1997-06</t>
+          <t>1997-04</t>
         </is>
       </c>
       <c r="N69" t="n">
@@ -13711,12 +13811,12 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>1997-07-01</t>
+          <t>1997-05-01</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>1997-07</t>
+          <t>1997-05</t>
         </is>
       </c>
       <c r="N70" t="n">
@@ -13856,12 +13956,12 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>1997-07-01</t>
+          <t>1997-05-01</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>1997-07</t>
+          <t>1997-05</t>
         </is>
       </c>
       <c r="N71" t="n">
@@ -14012,12 +14112,12 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>1997-07-01</t>
+          <t>1997-05-01</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>1997-07</t>
+          <t>1997-05</t>
         </is>
       </c>
       <c r="N72" t="n">
@@ -14246,12 +14346,12 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>1997-08-01</t>
+          <t>1997-06-01</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>1997-08</t>
+          <t>1997-06</t>
         </is>
       </c>
       <c r="N73" t="n">
@@ -14391,12 +14491,12 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>1997-08-01</t>
+          <t>1997-06-01</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>1997-08</t>
+          <t>1997-06</t>
         </is>
       </c>
       <c r="N74" t="n">
@@ -14547,12 +14647,12 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>1997-08-01</t>
+          <t>1997-06-01</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>1997-08</t>
+          <t>1997-06</t>
         </is>
       </c>
       <c r="N75" t="n">
@@ -14781,12 +14881,12 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>1997-09-01</t>
+          <t>1997-07-01</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>1997-09</t>
+          <t>1997-07</t>
         </is>
       </c>
       <c r="N76" t="n">
@@ -14926,12 +15026,12 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>1997-09-01</t>
+          <t>1997-07-01</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>1997-09</t>
+          <t>1997-07</t>
         </is>
       </c>
       <c r="N77" t="n">
@@ -15082,12 +15182,12 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>1997-09-01</t>
+          <t>1997-07-01</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>1997-09</t>
+          <t>1997-07</t>
         </is>
       </c>
       <c r="N78" t="n">
@@ -15316,12 +15416,12 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>1997-10-01</t>
+          <t>1997-08-01</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>1997-10</t>
+          <t>1997-08</t>
         </is>
       </c>
       <c r="N79" t="n">
@@ -15461,12 +15561,12 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>1997-10-01</t>
+          <t>1997-08-01</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>1997-10</t>
+          <t>1997-08</t>
         </is>
       </c>
       <c r="N80" t="n">
@@ -15617,12 +15717,12 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>1997-10-01</t>
+          <t>1997-08-01</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>1997-10</t>
+          <t>1997-08</t>
         </is>
       </c>
       <c r="N81" t="n">
@@ -15851,12 +15951,12 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>1997-11-01</t>
+          <t>1997-09-01</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>1997-11</t>
+          <t>1997-09</t>
         </is>
       </c>
       <c r="N82" t="n">
@@ -15996,19 +16096,19 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>1997-11-01</t>
+          <t>1997-09-01</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>1997-11</t>
+          <t>1997-09</t>
         </is>
       </c>
       <c r="N83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S83" t="inlineStr">
         <is>
@@ -16152,19 +16252,19 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>1997-11-01</t>
+          <t>1997-09-01</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>1997-11</t>
+          <t>1997-09</t>
         </is>
       </c>
       <c r="N84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U84" t="inlineStr">
         <is>
@@ -16386,19 +16486,19 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>1997-12-01</t>
+          <t>1997-10-01</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>1997-12</t>
+          <t>1997-10</t>
         </is>
       </c>
       <c r="N85" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O85" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q85" t="n">
         <v>0</v>
@@ -16531,12 +16631,12 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>1997-12-01</t>
+          <t>1997-10-01</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>1997-12</t>
+          <t>1997-10</t>
         </is>
       </c>
       <c r="N86" t="n">
@@ -16687,12 +16787,12 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>1997-12-01</t>
+          <t>1997-10-01</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>1997-12</t>
+          <t>1997-10</t>
         </is>
       </c>
       <c r="N87" t="n">
@@ -16921,12 +17021,12 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>1998-01-01</t>
+          <t>1997-11-01</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>1998-01</t>
+          <t>1997-11</t>
         </is>
       </c>
       <c r="N88" t="n">
@@ -17036,12 +17136,12 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -17066,19 +17166,19 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>1998-01-01</t>
+          <t>1997-11-01</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>1998-01</t>
+          <t>1997-11</t>
         </is>
       </c>
       <c r="N89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S89" t="inlineStr">
         <is>
@@ -17087,12 +17187,12 @@
       </c>
       <c r="U89" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_LEPROSY_ANNUAL</t>
+          <t>SER_NO_FHI_503_MONTHLY</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>annual</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO89" t="inlineStr">
@@ -17112,7 +17212,7 @@
       </c>
       <c r="AS89" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_LEPROSY_ANNUAL</t>
+          <t>SER_NO_FHI_503_MONTHLY</t>
         </is>
       </c>
       <c r="AT89" t="n">
@@ -17125,42 +17225,42 @@
       </c>
       <c r="AV89" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA89" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB89" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC89" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -17192,12 +17292,12 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -17222,38 +17322,38 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>1998-01-01</t>
+          <t>1997-11-01</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>1998-01</t>
+          <t>1997-11</t>
         </is>
       </c>
       <c r="N90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U90" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_LEPROSY_ANNUAL</t>
+          <t>SER_NO_FHI_503_MONTHLY</t>
         </is>
       </c>
       <c r="V90" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_LEPROSY_ANNUAL</t>
+          <t>SER_NO_FHI_503_MONTHLY</t>
         </is>
       </c>
       <c r="W90" t="inlineStr">
         <is>
-          <t>SRC_IS_DOH_HISTORY</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>Holdsveiki</t>
+          <t>Lepra</t>
         </is>
       </c>
       <c r="Y90" t="inlineStr">
@@ -17263,12 +17363,12 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>national_registry_notifications</t>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>annual</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AB90" t="inlineStr">
@@ -17278,7 +17378,7 @@
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>country:IS:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD90" t="inlineStr">
@@ -17303,7 +17403,7 @@
       </c>
       <c r="AH90" t="inlineStr">
         <is>
-          <t>historical</t>
+          <t>active</t>
         </is>
       </c>
       <c r="AI90" t="inlineStr">
@@ -17313,12 +17413,12 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>IS_DOH_historical_registry_annual</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK90" t="inlineStr">
         <is>
-          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
         </is>
       </c>
       <c r="AM90" t="inlineStr">
@@ -17346,7 +17446,7 @@
       </c>
       <c r="AS90" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_LEPROSY_ANNUAL</t>
+          <t>SER_NO_FHI_503_MONTHLY</t>
         </is>
       </c>
       <c r="AT90" t="n">
@@ -17359,42 +17459,42 @@
       </c>
       <c r="AV90" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA90" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB90" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC90" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -17456,19 +17556,19 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>1998-02-01</t>
+          <t>1997-12-01</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>1998-02</t>
+          <t>1997-12</t>
         </is>
       </c>
       <c r="N91" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O91" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q91" t="n">
         <v>0</v>
@@ -17571,12 +17671,12 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -17601,12 +17701,12 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>1998-03-01</t>
+          <t>1997-12-01</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>1998-03</t>
+          <t>1997-12</t>
         </is>
       </c>
       <c r="N92" t="n">
@@ -17615,76 +17715,87 @@
       <c r="O92" t="n">
         <v>0</v>
       </c>
-      <c r="Q92" t="n">
-        <v>0</v>
-      </c>
       <c r="S92" t="inlineStr">
         <is>
           <t>missing_population</t>
         </is>
       </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_503_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO92" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP92" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR92" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS92" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ92" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS92" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_503_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU92" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV92" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA92" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB92" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC92" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -17711,17 +17822,17 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -17746,90 +17857,179 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>1998-04-01</t>
+          <t>1997-12-01</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>1998-04</t>
+          <t>1997-12</t>
         </is>
       </c>
       <c r="N93" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O93" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q93" t="n">
-        <v>0</v>
-      </c>
-      <c r="S93" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_503_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_503_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>Lepra</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD93" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE93" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF93" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG93" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH93" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI93" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ93" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK93" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM93" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN93" t="b">
+        <v>1</v>
       </c>
       <c r="AO93" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP93" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR93" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS93" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ93" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS93" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_503_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU93" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV93" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA93" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB93" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC93" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -17861,12 +18061,12 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -17891,90 +18091,101 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>1998-05-01</t>
+          <t>1998-01-01</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>1998-05</t>
+          <t>1998-01</t>
         </is>
       </c>
       <c r="N94" t="n">
+        <v>7</v>
+      </c>
+      <c r="O94" t="n">
+        <v>7</v>
+      </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D64_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AO94" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP94" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ94" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS94" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D64_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT94" t="n">
         <v>1</v>
       </c>
-      <c r="O94" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q94" t="n">
-        <v>0</v>
-      </c>
-      <c r="S94" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
-      <c r="AO94" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP94" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR94" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS94" t="inlineStr"/>
-      <c r="AT94" t="n">
-        <v>0</v>
-      </c>
       <c r="AU94" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV94" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA94" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB94" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC94" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -18001,17 +18212,17 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -18036,90 +18247,179 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>1998-06-01</t>
+          <t>1998-01-01</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>1998-06</t>
+          <t>1998-01</t>
         </is>
       </c>
       <c r="N95" t="n">
+        <v>7</v>
+      </c>
+      <c r="O95" t="n">
+        <v>7</v>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D64_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D64_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>SRC_CA_PHAC_CNDSS</t>
+        </is>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>Leprosy</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>provincial_territorial_voluntary_notifications_national</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>country:CA:national</t>
+        </is>
+      </c>
+      <c r="AD95" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE95" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF95" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG95" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH95" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI95" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ95" t="inlineStr">
+        <is>
+          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK95" t="inlineStr">
+        <is>
+          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
+        </is>
+      </c>
+      <c r="AM95" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN95" t="b">
         <v>1</v>
       </c>
-      <c r="O95" t="n">
+      <c r="AO95" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP95" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ95" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS95" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D64_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT95" t="n">
         <v>1</v>
       </c>
-      <c r="Q95" t="n">
-        <v>0</v>
-      </c>
-      <c r="S95" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
-      <c r="AO95" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP95" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR95" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS95" t="inlineStr"/>
-      <c r="AT95" t="n">
-        <v>0</v>
-      </c>
       <c r="AU95" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV95" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA95" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB95" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC95" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -18181,12 +18481,12 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>1998-07-01</t>
+          <t>1998-01-01</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>1998-07</t>
+          <t>1998-01</t>
         </is>
       </c>
       <c r="N96" t="n">
@@ -18296,12 +18596,12 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -18326,90 +18626,101 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>1998-08-01</t>
+          <t>1998-01-01</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>1998-08</t>
+          <t>1998-01</t>
         </is>
       </c>
       <c r="N97" t="n">
+        <v>0</v>
+      </c>
+      <c r="O97" t="n">
+        <v>0</v>
+      </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_LEPROSY_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AO97" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP97" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ97" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS97" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_LEPROSY_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT97" t="n">
         <v>1</v>
       </c>
-      <c r="O97" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q97" t="n">
-        <v>0</v>
-      </c>
-      <c r="S97" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
-      <c r="AO97" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP97" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR97" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS97" t="inlineStr"/>
-      <c r="AT97" t="n">
-        <v>0</v>
-      </c>
       <c r="AU97" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV97" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA97" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB97" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC97" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -18436,17 +18747,17 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -18471,90 +18782,179 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>1998-09-01</t>
+          <t>1998-01-01</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>1998-09</t>
+          <t>1998-01</t>
         </is>
       </c>
       <c r="N98" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O98" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q98" t="n">
-        <v>0</v>
-      </c>
-      <c r="S98" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_LEPROSY_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_LEPROSY_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_HISTORY</t>
+        </is>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>Holdsveiki</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z98" t="inlineStr">
+        <is>
+          <t>national_registry_notifications</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB98" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD98" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE98" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF98" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG98" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH98" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI98" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ98" t="inlineStr">
+        <is>
+          <t>IS_DOH_historical_registry_annual</t>
+        </is>
+      </c>
+      <c r="AK98" t="inlineStr">
+        <is>
+          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM98" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN98" t="b">
+        <v>1</v>
       </c>
       <c r="AO98" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP98" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR98" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS98" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ98" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS98" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_LEPROSY_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU98" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV98" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA98" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB98" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC98" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -18616,12 +19016,12 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>1998-10-01</t>
+          <t>1998-02-01</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>1998-10</t>
+          <t>1998-02</t>
         </is>
       </c>
       <c r="N99" t="n">
@@ -18761,12 +19161,12 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>1998-11-01</t>
+          <t>1998-03-01</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>1998-11</t>
+          <t>1998-03</t>
         </is>
       </c>
       <c r="N100" t="n">
@@ -18906,19 +19306,19 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>1998-12-01</t>
+          <t>1998-04-01</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>1998-12</t>
+          <t>1998-04</t>
         </is>
       </c>
       <c r="N101" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O101" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q101" t="n">
         <v>0</v>
@@ -19051,19 +19451,19 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>1999-01-01</t>
+          <t>1998-05-01</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>1999-01</t>
+          <t>1998-05</t>
         </is>
       </c>
       <c r="N102" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O102" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q102" t="n">
         <v>0</v>
@@ -19166,12 +19566,12 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -19196,18 +19596,21 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>1999-01-01</t>
+          <t>1998-06-01</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>1999-01</t>
+          <t>1998-06</t>
         </is>
       </c>
       <c r="N103" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O103" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q103" t="n">
         <v>0</v>
       </c>
       <c r="S103" t="inlineStr">
@@ -19215,82 +19618,68 @@
           <t>missing_population</t>
         </is>
       </c>
-      <c r="U103" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_LEPROSY_ANNUAL</t>
-        </is>
-      </c>
-      <c r="AA103" t="inlineStr">
-        <is>
-          <t>annual</t>
-        </is>
-      </c>
       <c r="AO103" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP103" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ103" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS103" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_LEPROSY_ANNUAL</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR103" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS103" t="inlineStr"/>
       <c r="AT103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU103" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV103" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA103" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB103" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC103" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -19317,17 +19706,17 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -19352,12 +19741,12 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>1999-01-01</t>
+          <t>1998-07-01</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>1999-01</t>
+          <t>1998-07</t>
         </is>
       </c>
       <c r="N104" t="n">
@@ -19366,165 +19755,76 @@
       <c r="O104" t="n">
         <v>0</v>
       </c>
-      <c r="U104" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_LEPROSY_ANNUAL</t>
-        </is>
-      </c>
-      <c r="V104" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_LEPROSY_ANNUAL</t>
-        </is>
-      </c>
-      <c r="W104" t="inlineStr">
-        <is>
-          <t>SRC_IS_DOH_HISTORY</t>
-        </is>
-      </c>
-      <c r="X104" t="inlineStr">
-        <is>
-          <t>Holdsveiki</t>
-        </is>
-      </c>
-      <c r="Y104" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z104" t="inlineStr">
-        <is>
-          <t>national_registry_notifications</t>
-        </is>
-      </c>
-      <c r="AA104" t="inlineStr">
-        <is>
-          <t>annual</t>
-        </is>
-      </c>
-      <c r="AB104" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC104" t="inlineStr">
-        <is>
-          <t>country:IS:national</t>
-        </is>
-      </c>
-      <c r="AD104" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE104" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF104" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG104" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH104" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI104" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ104" t="inlineStr">
-        <is>
-          <t>IS_DOH_historical_registry_annual</t>
-        </is>
-      </c>
-      <c r="AK104" t="inlineStr">
-        <is>
-          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
-        </is>
-      </c>
-      <c r="AM104" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN104" t="b">
-        <v>1</v>
+      <c r="Q104" t="n">
+        <v>0</v>
+      </c>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
       </c>
       <c r="AO104" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP104" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ104" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS104" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_LEPROSY_ANNUAL</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR104" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS104" t="inlineStr"/>
       <c r="AT104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU104" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV104" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA104" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB104" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC104" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -19586,12 +19886,12 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>1999-02-01</t>
+          <t>1998-08-01</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>1999-02</t>
+          <t>1998-08</t>
         </is>
       </c>
       <c r="N105" t="n">
@@ -19731,19 +20031,19 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>1999-03-01</t>
+          <t>1998-09-01</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>1999-03</t>
+          <t>1998-09</t>
         </is>
       </c>
       <c r="N106" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O106" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q106" t="n">
         <v>0</v>
@@ -19876,19 +20176,19 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>1999-04-01</t>
+          <t>1998-10-01</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>1999-04</t>
+          <t>1998-10</t>
         </is>
       </c>
       <c r="N107" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O107" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q107" t="n">
         <v>0</v>
@@ -20021,19 +20321,19 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>1999-05-01</t>
+          <t>1998-11-01</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>1999-05</t>
+          <t>1998-11</t>
         </is>
       </c>
       <c r="N108" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O108" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q108" t="n">
         <v>0</v>
@@ -20166,19 +20466,19 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>1999-06-01</t>
+          <t>1998-12-01</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>1999-06</t>
+          <t>1998-12</t>
         </is>
       </c>
       <c r="N109" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O109" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q109" t="n">
         <v>0</v>
@@ -20281,12 +20581,12 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -20311,90 +20611,101 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>1999-07-01</t>
+          <t>1999-01-01</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>1999-07</t>
+          <t>1999-01</t>
         </is>
       </c>
       <c r="N110" t="n">
+        <v>10</v>
+      </c>
+      <c r="O110" t="n">
+        <v>10</v>
+      </c>
+      <c r="S110" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D64_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AO110" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP110" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ110" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS110" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D64_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT110" t="n">
         <v>1</v>
       </c>
-      <c r="O110" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q110" t="n">
-        <v>0</v>
-      </c>
-      <c r="S110" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
-      <c r="AO110" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP110" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR110" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS110" t="inlineStr"/>
-      <c r="AT110" t="n">
-        <v>0</v>
-      </c>
       <c r="AU110" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV110" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ110" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA110" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB110" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC110" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -20421,17 +20732,17 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -20456,90 +20767,179 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>1999-08-01</t>
+          <t>1999-01-01</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>1999-08</t>
+          <t>1999-01</t>
         </is>
       </c>
       <c r="N111" t="n">
+        <v>10</v>
+      </c>
+      <c r="O111" t="n">
+        <v>10</v>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D64_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D64_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W111" t="inlineStr">
+        <is>
+          <t>SRC_CA_PHAC_CNDSS</t>
+        </is>
+      </c>
+      <c r="X111" t="inlineStr">
+        <is>
+          <t>Leprosy</t>
+        </is>
+      </c>
+      <c r="Y111" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z111" t="inlineStr">
+        <is>
+          <t>provincial_territorial_voluntary_notifications_national</t>
+        </is>
+      </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB111" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC111" t="inlineStr">
+        <is>
+          <t>country:CA:national</t>
+        </is>
+      </c>
+      <c r="AD111" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE111" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF111" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG111" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH111" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI111" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ111" t="inlineStr">
+        <is>
+          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK111" t="inlineStr">
+        <is>
+          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
+        </is>
+      </c>
+      <c r="AM111" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN111" t="b">
         <v>1</v>
       </c>
-      <c r="O111" t="n">
+      <c r="AO111" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP111" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ111" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS111" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D64_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT111" t="n">
         <v>1</v>
       </c>
-      <c r="Q111" t="n">
-        <v>0</v>
-      </c>
-      <c r="S111" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
-      <c r="AO111" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP111" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR111" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS111" t="inlineStr"/>
-      <c r="AT111" t="n">
-        <v>0</v>
-      </c>
       <c r="AU111" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV111" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ111" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA111" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB111" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC111" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -20601,19 +21001,19 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>1999-09-01</t>
+          <t>1999-01-01</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>1999-09</t>
+          <t>1999-01</t>
         </is>
       </c>
       <c r="N112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q112" t="n">
         <v>0</v>
@@ -20716,12 +21116,12 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -20746,90 +21146,101 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>1999-10-01</t>
+          <t>1999-01-01</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>1999-10</t>
+          <t>1999-01</t>
         </is>
       </c>
       <c r="N113" t="n">
+        <v>0</v>
+      </c>
+      <c r="O113" t="n">
+        <v>0</v>
+      </c>
+      <c r="S113" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_LEPROSY_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AO113" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP113" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ113" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS113" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_LEPROSY_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT113" t="n">
         <v>1</v>
       </c>
-      <c r="O113" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q113" t="n">
-        <v>0</v>
-      </c>
-      <c r="S113" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
-      <c r="AO113" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP113" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR113" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS113" t="inlineStr"/>
-      <c r="AT113" t="n">
-        <v>0</v>
-      </c>
       <c r="AU113" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV113" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ113" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA113" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB113" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC113" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -20856,17 +21267,17 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -20891,90 +21302,179 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>1999-11-01</t>
+          <t>1999-01-01</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>1999-11</t>
+          <t>1999-01</t>
         </is>
       </c>
       <c r="N114" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O114" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q114" t="n">
-        <v>0</v>
-      </c>
-      <c r="S114" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_LEPROSY_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_LEPROSY_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_HISTORY</t>
+        </is>
+      </c>
+      <c r="X114" t="inlineStr">
+        <is>
+          <t>Holdsveiki</t>
+        </is>
+      </c>
+      <c r="Y114" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z114" t="inlineStr">
+        <is>
+          <t>national_registry_notifications</t>
+        </is>
+      </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB114" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD114" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE114" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF114" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG114" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH114" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI114" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ114" t="inlineStr">
+        <is>
+          <t>IS_DOH_historical_registry_annual</t>
+        </is>
+      </c>
+      <c r="AK114" t="inlineStr">
+        <is>
+          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM114" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN114" t="b">
+        <v>1</v>
       </c>
       <c r="AO114" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP114" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR114" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS114" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ114" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS114" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_LEPROSY_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU114" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV114" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ114" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA114" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB114" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC114" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -21036,19 +21536,19 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>1999-12-01</t>
+          <t>1999-02-01</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>1999-12</t>
+          <t>1999-02</t>
         </is>
       </c>
       <c r="N115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q115" t="n">
         <v>0</v>
@@ -21118,6 +21618,1456 @@
         </is>
       </c>
       <c r="BC115" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>D042</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>leprosy</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Leprosy</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>D042</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>Leprosy</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>麻风病</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>1999-03-01</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>1999-03</t>
+        </is>
+      </c>
+      <c r="N116" t="n">
+        <v>0</v>
+      </c>
+      <c r="O116" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q116" t="n">
+        <v>0</v>
+      </c>
+      <c r="S116" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO116" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP116" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR116" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS116" t="inlineStr"/>
+      <c r="AT116" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU116" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV116" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW116" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX116" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY116" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA116" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB116" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC116" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>D042</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>leprosy</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Leprosy</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>D042</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>Leprosy</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>麻风病</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>1999-04-01</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>1999-04</t>
+        </is>
+      </c>
+      <c r="N117" t="n">
+        <v>3</v>
+      </c>
+      <c r="O117" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0</v>
+      </c>
+      <c r="S117" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO117" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP117" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR117" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS117" t="inlineStr"/>
+      <c r="AT117" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU117" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV117" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW117" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX117" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY117" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA117" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB117" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC117" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>D042</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>leprosy</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Leprosy</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>D042</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>Leprosy</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>麻风病</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>1999-05-01</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>1999-05</t>
+        </is>
+      </c>
+      <c r="N118" t="n">
+        <v>2</v>
+      </c>
+      <c r="O118" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0</v>
+      </c>
+      <c r="S118" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO118" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP118" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR118" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS118" t="inlineStr"/>
+      <c r="AT118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU118" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV118" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW118" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX118" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY118" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA118" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB118" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC118" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>D042</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>leprosy</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Leprosy</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>D042</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>Leprosy</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>麻风病</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>1999-06-01</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>1999-06</t>
+        </is>
+      </c>
+      <c r="N119" t="n">
+        <v>0</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0</v>
+      </c>
+      <c r="S119" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO119" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP119" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR119" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS119" t="inlineStr"/>
+      <c r="AT119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU119" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV119" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW119" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX119" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY119" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA119" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB119" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC119" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>D042</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>leprosy</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Leprosy</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>D042</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>Leprosy</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>麻风病</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>1999-07-01</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>1999-07</t>
+        </is>
+      </c>
+      <c r="N120" t="n">
+        <v>1</v>
+      </c>
+      <c r="O120" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0</v>
+      </c>
+      <c r="S120" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO120" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP120" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR120" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS120" t="inlineStr"/>
+      <c r="AT120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU120" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV120" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW120" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX120" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY120" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA120" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB120" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC120" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>D042</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>leprosy</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Leprosy</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>D042</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>Leprosy</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>麻风病</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>1999-08-01</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>1999-08</t>
+        </is>
+      </c>
+      <c r="N121" t="n">
+        <v>1</v>
+      </c>
+      <c r="O121" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0</v>
+      </c>
+      <c r="S121" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO121" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP121" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR121" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS121" t="inlineStr"/>
+      <c r="AT121" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU121" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV121" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW121" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX121" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY121" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA121" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB121" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC121" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>D042</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>leprosy</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Leprosy</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>D042</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>Leprosy</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>麻风病</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>1999-09-01</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>1999-09</t>
+        </is>
+      </c>
+      <c r="N122" t="n">
+        <v>1</v>
+      </c>
+      <c r="O122" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0</v>
+      </c>
+      <c r="S122" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO122" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP122" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR122" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS122" t="inlineStr"/>
+      <c r="AT122" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU122" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV122" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW122" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX122" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY122" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA122" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB122" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC122" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>D042</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>leprosy</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Leprosy</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>D042</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>Leprosy</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>麻风病</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>1999-10-01</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>1999-10</t>
+        </is>
+      </c>
+      <c r="N123" t="n">
+        <v>1</v>
+      </c>
+      <c r="O123" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0</v>
+      </c>
+      <c r="S123" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO123" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP123" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR123" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS123" t="inlineStr"/>
+      <c r="AT123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU123" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV123" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW123" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX123" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY123" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA123" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB123" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC123" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>D042</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>leprosy</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Leprosy</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>D042</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>Leprosy</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>麻风病</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>1999-11-01</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>1999-11</t>
+        </is>
+      </c>
+      <c r="N124" t="n">
+        <v>4</v>
+      </c>
+      <c r="O124" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0</v>
+      </c>
+      <c r="S124" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO124" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP124" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR124" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS124" t="inlineStr"/>
+      <c r="AT124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU124" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV124" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW124" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX124" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY124" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA124" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB124" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC124" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>D042</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>leprosy</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Leprosy</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>D042</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>Leprosy</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>麻风病</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>1999-12-01</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>1999-12</t>
+        </is>
+      </c>
+      <c r="N125" t="n">
+        <v>0</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0</v>
+      </c>
+      <c r="S125" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO125" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP125" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR125" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS125" t="inlineStr"/>
+      <c r="AT125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU125" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV125" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW125" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX125" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY125" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA125" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB125" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC125" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
@@ -21239,7 +23189,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
     </row>
     <row r="10">
@@ -21249,7 +23199,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>114</v>
+        <v>124</v>
       </c>
     </row>
     <row r="11">
@@ -21269,7 +23219,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="13">
@@ -21279,7 +23229,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -21301,7 +23251,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>42</v>
+        <v>85</v>
       </c>
     </row>
     <row r="16">
